--- a/Tech_Company_Oil_Exposure_Analysis.xlsx
+++ b/Tech_Company_Oil_Exposure_Analysis.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sources &amp; Methodology" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Revenue &amp; Backlog Exposure'!$A$3:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Revenue &amp; Backlog Exposure'!$A$3:$K$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -849,176 +849,281 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Ride-Hailing Impact</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Uber/Lyft fares rose 9.6% in 2025; 60% of riders cutting back. Fuel is the largest driver variable cost.</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Travel Platforms</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Booking Holdings ($26.9B rev), Expedia ($14.7B), Airbnb ($12.2B) face indirect oil exposure via airline fuel surcharges and travel demand elasticity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>E-commerce/Marketplace</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Shopify ($378B GMV), MercadoLibre (+39% rev), eBay, Etsy exposed through shipping cost inflation passed to merchants and buyers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>HOW HIGH OIL PRICES AFFECT TECH COMPANIES</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Mechanism</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Primary Victims</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Direct Cost Inflation</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Oil used in plastics/chemicals for hardware; transportation/logistics costs rise</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Hardware OEMs, E-commerce (Amazon, Apple)</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Data Center Energy Costs</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Natural gas prices spike electricity costs; 100MW data center costs $900M-$1.5B to build</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>AWS, Azure, Google Cloud, Meta</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Interest Rate Pressure</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Oil inflation forces central bank tightening; discount rates rise, compressing growth multiples</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>High-multiple SaaS (CRM, NOW, DDOG)</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Enterprise Budget Cuts</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Companies enter cost-control mode; discretionary software spend deferred</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Mid-market SaaS, consulting firms</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Supply Chain Disruption</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Strait of Hormuz risk; shipping costs rise; component availability affected</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Semis (NVDA, TSM, MU), hardware</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Consumer Spending Drag</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Goldman: 0.2% drag on consumer spend; lower-income hit hardest</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Ad-driven (Alphabet, Meta), e-commerce</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Ride-Hail / Delivery Fuel</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Fuel is largest variable cost for drivers; surcharges passed to riders reduce demand</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Uber, Lyft, DoorDash — fares rose 9.6% in 2025</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Travel Demand Erosion</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Airline fuel surcharges raise travel costs; consumers defer discretionary travel</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Booking, Expedia, Airbnb — elastic demand</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Marketplace Shipping</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Higher fuel raises shipping/logistics; sellers pass costs to buyers, compressing GMV</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Shopify, eBay, Etsy, MercadoLibre</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B13:H13"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1032,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2093,107 +2198,767 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Ride-Hailing / Delivery</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>130.5</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>5.2</v>
+        <v>57.4</v>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>~4%</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="n">
-        <v>8</v>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>~5%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>AI chips used in energy sector. Down 1.74% in March 2026 energy shock.</t>
+          <t>Fares rose 9.6% in 2025 (fuel + platform fees). 60% of riders cutting back. $193B gross bookings. $10B FCF.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Delivery Marketplace</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Delivery logistics directly tied to fuel costs. $101B marketplace GOV. GAAP net income $935M in FY25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Ride-Hailing</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>$18.2B gross bookings. Driver costs rise with fuel; fares passed to consumers. $1.1B FCF in FY25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Booking Holdings</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Online Travel</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>$41.9B gross bookings Q4. Airline fuel surcharges raise travel costs, dampening demand. Flight bookings +38% YoY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Online Travel</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>$12.2B revenue (+10.3% YoY). Less fuel-exposed than airlines/hotels but travel demand elastic to macro shocks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Online Travel</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Cautious 2026 guidance citing 'uneven' consumer spend. U.S. pricing softness. Airline fuel surcharges pass through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>E-commerce Platform</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>$378.4B GMV (+29%). Merchants' shipping costs rise with oil. $2B FCF. 30% revenue growth in FY25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Online Marketplace</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>$21.2B GMV in Q4 (+10%). Shipping costs borne by sellers/buyers. 26.1% non-GAAP operating margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Etsy</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Online Marketplace</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>$3.6B marketplace GMS. Expanded 3P shipping in 5 EU markets. De minimis exemption risk. 25.2% adj. EBITDA margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>MercadoLibre</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>LatAm E-commerce</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>Revenue +39% YoY. Fulfillment network delivers 75% shipments in &lt;48h. Brazil unit shipping costs fell 8% QoQ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Social / Discovery</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J33" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>619M MAUs. Ad-driven model; oil impact via consumer spend drag and advertiser budget sensitivity. 30% adj. EBITDA margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>Revenue +11% YoY. Ad-driven; exposed to macro-driven ad budget cuts. Net loss narrowed to $460M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>~4%</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>~5%</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>AI chips used in energy sector. Down 1.74% in March 2026 energy shock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
           <t>Taiwan Semiconductor</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>TSM</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D36" s="8" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E36" s="8" t="n">
         <v>2.6</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>~3%</t>
         </is>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G36" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>~3%</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Low-Moderate</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>Fab costs sensitive to energy prices. Down 4.44% in March 2026 selloff.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K24"/>
+  <autoFilter ref="A3:K36"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -3111,7 +3876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3707,27 +4472,27 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Amazon (AWS)</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>~2%</t>
+          <t>Indirect</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>~3%</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Cloud / E-commerce</t>
+          <t>Ride-Hailing / Delivery</t>
         </is>
       </c>
     </row>
@@ -3737,27 +4502,27 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Alphabet (Google Cloud)</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>~1.4%</t>
+          <t>Indirect</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>~2%</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Cloud / Internet</t>
+          <t>Delivery Marketplace</t>
         </is>
       </c>
     </row>
@@ -3767,25 +4532,385 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Ride-Hailing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Booking Holdings</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Online Travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Online Travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>MercadoLibre</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>LatAm E-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>E-commerce Platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Online Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Online Travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Etsy</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Online Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Amazon (AWS + E-commerce)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>~2%</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>~3%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Cloud / E-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Alphabet (Google Cloud)</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>~1.4%</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>~2%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Cloud / Internet</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Social / Discovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t>Meta Platforms</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>~0.3%</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>Low-Medium</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>Internet / Social</t>
         </is>
@@ -3806,7 +4931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4002,75 +5127,257 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr"/>
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 Earnings - $57.4B revenue, $193B gross bookings, $10B FCF. Fares +9.6% YoY.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="inlineStr">
         <is>
-          <t>Methodology Notes</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 Earnings - $13.7B revenue, $101B marketplace GOV, $935M GAAP net income</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>Revenue Exposure</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Where companies do not break out oil/gas specifically, estimates are based on industry segment reports (e.g., 'Resources' or 'Energy, Utilities, Resources') and may include adjacent verticals (utilities, chemicals, mining). Figures marked with '~' are estimates.</t>
+          <t>FY2025 Earnings - $18.2B gross bookings, $1.1B FCF, $528.8M adj. EBITDA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Backlog estimates for pure-play oilfield tech companies are based on reported order books. For IT services and enterprise software companies, backlog is estimated from remaining performance obligations and deal pipeline disclosures.</t>
+          <t>FY2025 10-K - $26.9B revenue, $41.9B Q4 gross bookings, flight bookings +38%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 Earnings - $12.2B revenue (+10.3% YoY), $72.9B gross booking value</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 Earnings - $14.7B revenue (+8% YoY), cautious 2026 guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 Earnings - $11.6B revenue (+30%), $378.4B GMV, $2B FCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Q4 2025 Earnings - $3.0B quarterly revenue (+15%), $21.2B GMV (+10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Etsy</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 Earnings - $881.6M revenue (+6.6% ex-Reverb), $3.6B marketplace GMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>MercadoLibre</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 Earnings - Revenue +39% YoY, $19.9B Q4 GMV. Brazil shipping costs -8% QoQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 Earnings - $4.2B revenue (+16%), 619M MAUs, 30% adj. EBITDA margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 Earnings - $5.9B revenue (+11%), $689M adj. EBITDA, net loss $460M</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Benzinga / Business Insider</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Uber &amp; Lyft fare analysis: 9.6% increase in 2025; 60.4% of riders cutting back</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Methodology Notes</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Revenue Exposure</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Where companies do not break out oil/gas specifically, estimates are based on industry segment reports (e.g., 'Resources' or 'Energy, Utilities, Resources') and may include adjacent verticals (utilities, chemicals, mining). Figures marked with '~' are estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Backlog estimates for pure-play oilfield tech companies are based on reported order books. For IT services and enterprise software companies, backlog is estimated from remaining performance obligations and deal pipeline disclosures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
           <t>Exposure Rating</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Composite rating considering: (1) energy revenue as % of total, (2) backlog concentration, (3) direct oil price sensitivity of business model, (4) ability to pass through costs.</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Indirect Exposure</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Internet and marketplace companies have 'Indirect' oil exposure — they do not sell to the oil/gas sector but are affected through fuel/shipping costs (ride-hailing, delivery, e-commerce), travel demand elasticity (OTAs), consumer spending drag (ad-driven), and data center energy costs. Ratings reflect the magnitude of these indirect transmission channels.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="35">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
